--- a/artfynd/A 53950-2019 artfynd.xlsx
+++ b/artfynd/A 53950-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126974677</v>
       </c>
       <c r="B2" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126974674</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126974675</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126974671</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126974676</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126974668</v>
       </c>
       <c r="B7" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126974672</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126974678</v>
       </c>
       <c r="B9" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
